--- a/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_4spot.xlsx
+++ b/plm python control/wrappers/multibeam parameters/Poincare beams/multiBeam_4spot.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\Poincare beams\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD40F4F-DD9F-4B8A-B7CE-F77BF2D9357C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CA297F-DE77-47EA-8D98-27B77167B909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14895" yWindow="870" windowWidth="12630" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18195" yWindow="975" windowWidth="7080" windowHeight="13860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -534,7 +534,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -736,7 +736,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="1">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -854,7 +854,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="1">
-        <v>11.235799999999999</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -868,7 +868,7 @@
         <v>4</v>
       </c>
       <c r="D33" s="1">
-        <v>11.64</v>
+        <v>12.77777777777778</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -882,7 +882,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="1">
-        <v>40.512</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -896,7 +896,7 @@
         <v>4</v>
       </c>
       <c r="D35" s="1">
-        <v>11.488</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -938,7 +938,7 @@
         <v>6</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -952,7 +952,7 @@
         <v>7</v>
       </c>
       <c r="D39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -966,7 +966,7 @@
         <v>7</v>
       </c>
       <c r="D40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -980,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="1">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1036,7 +1036,7 @@
         <v>9</v>
       </c>
       <c r="D45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1176,7 +1176,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
